--- a/jyx2/Assets/Mods/shendiao/Configs/场景.xlsx
+++ b/jyx2/Assets/Mods/shendiao/Configs/场景.xlsx
@@ -9,12 +9,12 @@
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="true"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="162">
   <si>
     <t>LuaConfigGen</t>
   </si>
@@ -221,18 +221,297 @@
   </si>
   <si>
     <t>WORLDMAP</t>
+  </si>
+  <si>
+    <t>破庙</t>
+  </si>
+  <si>
+    <t>62_pomiao</t>
+  </si>
+  <si>
+    <t>神雕山洞</t>
+  </si>
+  <si>
+    <t>07_shandong</t>
+  </si>
+  <si>
+    <t>POINTLIGHT</t>
+  </si>
+  <si>
+    <t>重阳宫</t>
+  </si>
+  <si>
+    <t>19_chongyanggong</t>
+  </si>
+  <si>
+    <t>古墓</t>
+  </si>
+  <si>
+    <t>18_gumu</t>
+  </si>
+  <si>
+    <t>22_jueqinggu</t>
+  </si>
+  <si>
+    <t>绝情谷底</t>
+  </si>
+  <si>
+    <t>80_jueqinggudi</t>
+  </si>
+  <si>
+    <t>百花谷</t>
+  </si>
+  <si>
+    <t>20_baihuagu</t>
+  </si>
+  <si>
+    <t>华山派</t>
+  </si>
+  <si>
+    <t>57_huashanpai</t>
+  </si>
+  <si>
+    <t>思过崖</t>
+  </si>
+  <si>
+    <t>81_siguoya</t>
+  </si>
+  <si>
+    <t>铁掌山</t>
+  </si>
+  <si>
+    <t>48_tiezhangshan</t>
+  </si>
+  <si>
+    <t>黑龙潭</t>
+  </si>
+  <si>
+    <t>21_heilongtan</t>
+  </si>
+  <si>
+    <t>NONAVAGENT</t>
+  </si>
+  <si>
+    <t>一灯居</t>
+  </si>
+  <si>
+    <t>47_yidengju</t>
+  </si>
+  <si>
+    <t>程英居</t>
+  </si>
+  <si>
+    <t>45_chengyingju</t>
+  </si>
+  <si>
+    <t>75_taohuadao</t>
+  </si>
+  <si>
+    <t>胡斐居〔未开放〕</t>
+  </si>
+  <si>
+    <t>河洛客栈〔未开放〕</t>
+  </si>
+  <si>
+    <t>云鹤崖〔未开放〕</t>
+  </si>
+  <si>
+    <t>有间客栈〔未开放〕</t>
+  </si>
+  <si>
+    <t>闯王山洞〔未开放〕</t>
+  </si>
+  <si>
+    <t>北丑居〔未开放〕</t>
+  </si>
+  <si>
+    <t>大轮寺〔未开放〕</t>
+  </si>
+  <si>
+    <t>成昆居〔未开放〕</t>
+  </si>
+  <si>
+    <t>蜘蛛山洞〔未开放〕</t>
+  </si>
+  <si>
+    <t>光明顶〔未开放〕</t>
+  </si>
+  <si>
+    <t>明教分舵〔未开放〕</t>
+  </si>
+  <si>
+    <t>沙漠废墟〔未开放〕</t>
+  </si>
+  <si>
+    <t>金轮寺〔未开放〕</t>
+  </si>
+  <si>
+    <t>回族部落〔未开放〕</t>
+  </si>
+  <si>
+    <t>洪七公居〔未开放〕</t>
+  </si>
+  <si>
+    <t>苗人凤居〔未开放〕</t>
+  </si>
+  <si>
+    <t>武道大会〔未开放〕</t>
+  </si>
+  <si>
+    <t>黑木崖〔未开放〕</t>
+  </si>
+  <si>
+    <t>嵩山派〔未开放〕</t>
+  </si>
+  <si>
+    <t>少林寺〔未开放〕</t>
+  </si>
+  <si>
+    <t>泰山派〔未开放〕</t>
+  </si>
+  <si>
+    <t>平一指居〔未开放〕</t>
+  </si>
+  <si>
+    <t>恒山派〔未开放〕</t>
+  </si>
+  <si>
+    <t>海边小屋〔未开放〕</t>
+  </si>
+  <si>
+    <t>峨嵋派〔未开放〕</t>
+  </si>
+  <si>
+    <t>崆峒派〔未开放〕</t>
+  </si>
+  <si>
+    <t>星宿海〔未开放〕</t>
+  </si>
+  <si>
+    <t>青城派〔未开放〕</t>
+  </si>
+  <si>
+    <t>五毒教〔未开放〕</t>
+  </si>
+  <si>
+    <t>摩天崖〔未开放〕</t>
+  </si>
+  <si>
+    <t>凌霄城〔未开放〕</t>
+  </si>
+  <si>
+    <t>悦来客栈〔未开放〕</t>
+  </si>
+  <si>
+    <t>神秘山洞〔未开放〕</t>
+  </si>
+  <si>
+    <t>无量山洞〔未开放〕</t>
+  </si>
+  <si>
+    <t>武当派〔未开放〕</t>
+  </si>
+  <si>
+    <t>蝴蝶谷〔未开放〕</t>
+  </si>
+  <si>
+    <t>金蛇山洞〔未开放〕</t>
+  </si>
+  <si>
+    <t>药王庄〔未开放〕</t>
+  </si>
+  <si>
+    <t>阎基居〔未开放〕</t>
+  </si>
+  <si>
+    <t>丐帮〔未开放〕</t>
+  </si>
+  <si>
+    <t>燕子坞〔未开放〕</t>
+  </si>
+  <si>
+    <t>擂鼓山〔未开放〕</t>
+  </si>
+  <si>
+    <t>薛慕华居〔未开放〕</t>
+  </si>
+  <si>
+    <t>梅庄〔未开放〕</t>
+  </si>
+  <si>
+    <t>福威镖局〔未开放〕</t>
+  </si>
+  <si>
+    <t>衡山派〔未开放〕</t>
+  </si>
+  <si>
+    <t>田伯光居〔未开放〕</t>
+  </si>
+  <si>
+    <t>龙门客栈〔未开放〕</t>
+  </si>
+  <si>
+    <t>高升客栈〔未开放〕</t>
+  </si>
+  <si>
+    <t>天宁寺〔未开放〕</t>
+  </si>
+  <si>
+    <t>南贤居〔未开放〕</t>
+  </si>
+  <si>
+    <t>唐诗山洞〔未开放〕</t>
+  </si>
+  <si>
+    <t>冰蚕山洞〔未开放〕</t>
+  </si>
+  <si>
+    <t>昆仑山洞〔未开放〕</t>
+  </si>
+  <si>
+    <t>昆仑派〔未开放〕</t>
+  </si>
+  <si>
+    <t>白驼山〔未开放〕</t>
+  </si>
+  <si>
+    <t>小虾米居〔未开放〕</t>
+  </si>
+  <si>
+    <t>神龙教〔未开放〕</t>
+  </si>
+  <si>
+    <t>冰火岛〔未开放〕</t>
+  </si>
+  <si>
+    <t>灵蛇岛〔未开放〕</t>
+  </si>
+  <si>
+    <t>侠客岛〔未开放〕</t>
+  </si>
+  <si>
+    <t>霹雳堂〔未开放〕</t>
+  </si>
+  <si>
+    <t>万鳄岛〔未开放〕</t>
+  </si>
+  <si>
+    <t>渤泥岛〔未开放〕</t>
+  </si>
+  <si>
+    <t>鸳鸯山洞〔未开放〕</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -263,12 +542,12 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -552,7 +831,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H84"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -646,19 +925,19 @@
         <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>69</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
       <c r="D5" t="s">
         <v>22</v>
       </c>
       <c r="E5">
-        <v>19</v>
+        <v>-1</v>
       </c>
       <c r="F5">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -672,19 +951,19 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>74</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="D6" t="s">
         <v>22</v>
       </c>
       <c r="E6">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F6">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -695,22 +974,25 @@
         <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>76</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>77</v>
       </c>
       <c r="D7" t="s">
         <v>22</v>
       </c>
       <c r="E7">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F7">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="G7">
         <v>0</v>
+      </c>
+      <c r="H7" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -718,22 +1000,25 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>71</v>
       </c>
       <c r="C8" t="s">
-        <v>29</v>
+        <v>72</v>
       </c>
       <c r="D8" t="s">
         <v>22</v>
       </c>
       <c r="E8">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F8">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="G8">
         <v>0</v>
+      </c>
+      <c r="H8" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -741,19 +1026,19 @@
         <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C9" t="s">
-        <v>31</v>
+        <v>78</v>
       </c>
       <c r="D9" t="s">
         <v>22</v>
       </c>
       <c r="E9">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="F9">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -764,19 +1049,19 @@
         <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>79</v>
       </c>
       <c r="C10" t="s">
-        <v>33</v>
+        <v>80</v>
       </c>
       <c r="D10" t="s">
         <v>22</v>
       </c>
       <c r="E10">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F10">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -787,19 +1072,19 @@
         <v>6</v>
       </c>
       <c r="B11" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="C11" t="s">
-        <v>35</v>
+        <v>82</v>
       </c>
       <c r="D11" t="s">
         <v>22</v>
       </c>
       <c r="E11">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F11">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -810,19 +1095,19 @@
         <v>7</v>
       </c>
       <c r="B12" t="s">
-        <v>36</v>
+        <v>83</v>
       </c>
       <c r="C12" t="s">
-        <v>37</v>
+        <v>84</v>
       </c>
       <c r="D12" t="s">
         <v>22</v>
       </c>
       <c r="E12">
-        <v>18</v>
+        <v>-1</v>
       </c>
       <c r="F12">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -833,19 +1118,19 @@
         <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="C13" t="s">
-        <v>39</v>
+        <v>86</v>
       </c>
       <c r="D13" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="E13">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F13">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -856,19 +1141,19 @@
         <v>9</v>
       </c>
       <c r="B14" t="s">
-        <v>41</v>
+        <v>87</v>
       </c>
       <c r="C14" t="s">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="D14" t="s">
         <v>22</v>
       </c>
       <c r="E14">
-        <v>15</v>
+        <v>-1</v>
       </c>
       <c r="F14">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -879,22 +1164,25 @@
         <v>10</v>
       </c>
       <c r="B15" t="s">
-        <v>43</v>
+        <v>89</v>
       </c>
       <c r="C15" t="s">
-        <v>44</v>
+        <v>90</v>
       </c>
       <c r="D15" t="s">
         <v>22</v>
       </c>
       <c r="E15">
+        <v>8</v>
+      </c>
+      <c r="F15">
         <v>16</v>
       </c>
-      <c r="F15">
-        <v>-1</v>
-      </c>
       <c r="G15">
         <v>0</v>
+      </c>
+      <c r="H15" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -902,19 +1190,19 @@
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>45</v>
+        <v>92</v>
       </c>
       <c r="C16" t="s">
-        <v>46</v>
+        <v>93</v>
       </c>
       <c r="D16" t="s">
         <v>22</v>
       </c>
       <c r="E16">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F16">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -925,19 +1213,19 @@
         <v>12</v>
       </c>
       <c r="B17" t="s">
-        <v>47</v>
+        <v>94</v>
       </c>
       <c r="C17" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="D17" t="s">
         <v>22</v>
       </c>
       <c r="E17">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F17">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -948,19 +1236,19 @@
         <v>13</v>
       </c>
       <c r="B18" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C18" t="s">
-        <v>50</v>
+        <v>96</v>
       </c>
       <c r="D18" t="s">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="E18">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="F18">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -968,165 +1256,1522 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19">
-        <v>14</v>
+        <v>100</v>
       </c>
       <c r="B19" t="s">
-        <v>52</v>
+        <v>97</v>
       </c>
       <c r="C19" t="s">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="D19" t="s">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="E19">
-        <v>9</v>
+        <v>-1</v>
       </c>
       <c r="F19">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20">
-        <v>15</v>
+        <v>101</v>
       </c>
       <c r="B20" t="s">
-        <v>55</v>
+        <v>98</v>
       </c>
       <c r="C20" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="D20" t="s">
-        <v>57</v>
+        <v>22</v>
       </c>
       <c r="E20">
         <v>-1</v>
       </c>
       <c r="F20">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21">
-        <v>16</v>
+        <v>102</v>
       </c>
       <c r="B21" t="s">
-        <v>58</v>
+        <v>99</v>
       </c>
       <c r="C21" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="D21" t="s">
         <v>22</v>
       </c>
       <c r="E21">
-        <v>11</v>
+        <v>-1</v>
       </c>
       <c r="F21">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22">
-        <v>17</v>
+        <v>103</v>
       </c>
       <c r="B22" t="s">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="C22" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="D22" t="s">
         <v>22</v>
       </c>
       <c r="E22">
-        <v>12</v>
+        <v>-1</v>
       </c>
       <c r="F22">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23">
-        <v>18</v>
+        <v>104</v>
       </c>
       <c r="B23" t="s">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="C23" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="D23" t="s">
         <v>22</v>
       </c>
       <c r="E23">
-        <v>9</v>
+        <v>-1</v>
       </c>
       <c r="F23">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24">
-        <v>19</v>
+        <v>105</v>
       </c>
       <c r="B24" t="s">
-        <v>64</v>
+        <v>102</v>
       </c>
       <c r="C24" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D24" t="s">
         <v>22</v>
       </c>
       <c r="E24">
-        <v>15</v>
+        <v>-1</v>
       </c>
       <c r="F24">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25">
+        <v>106</v>
+      </c>
+      <c r="B25" t="s">
+        <v>103</v>
+      </c>
+      <c r="C25" t="s">
+        <v>70</v>
+      </c>
+      <c r="D25" t="s">
+        <v>22</v>
+      </c>
+      <c r="E25">
+        <v>-1</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>107</v>
+      </c>
+      <c r="B26" t="s">
+        <v>104</v>
+      </c>
+      <c r="C26" t="s">
+        <v>70</v>
+      </c>
+      <c r="D26" t="s">
+        <v>22</v>
+      </c>
+      <c r="E26">
+        <v>-1</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>108</v>
+      </c>
+      <c r="B27" t="s">
+        <v>105</v>
+      </c>
+      <c r="C27" t="s">
+        <v>70</v>
+      </c>
+      <c r="D27" t="s">
+        <v>22</v>
+      </c>
+      <c r="E27">
+        <v>-1</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>109</v>
+      </c>
+      <c r="B28" t="s">
+        <v>106</v>
+      </c>
+      <c r="C28" t="s">
+        <v>70</v>
+      </c>
+      <c r="D28" t="s">
+        <v>22</v>
+      </c>
+      <c r="E28">
+        <v>-1</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>110</v>
+      </c>
+      <c r="B29" t="s">
+        <v>107</v>
+      </c>
+      <c r="C29" t="s">
+        <v>70</v>
+      </c>
+      <c r="D29" t="s">
+        <v>22</v>
+      </c>
+      <c r="E29">
+        <v>-1</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>111</v>
+      </c>
+      <c r="B30" t="s">
+        <v>108</v>
+      </c>
+      <c r="C30" t="s">
+        <v>70</v>
+      </c>
+      <c r="D30" t="s">
+        <v>22</v>
+      </c>
+      <c r="E30">
+        <v>-1</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>112</v>
+      </c>
+      <c r="B31" t="s">
+        <v>109</v>
+      </c>
+      <c r="C31" t="s">
+        <v>70</v>
+      </c>
+      <c r="D31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E31">
+        <v>-1</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>113</v>
+      </c>
+      <c r="B32" t="s">
+        <v>110</v>
+      </c>
+      <c r="C32" t="s">
+        <v>70</v>
+      </c>
+      <c r="D32" t="s">
+        <v>22</v>
+      </c>
+      <c r="E32">
+        <v>-1</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>114</v>
+      </c>
+      <c r="B33" t="s">
+        <v>111</v>
+      </c>
+      <c r="C33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D33" t="s">
+        <v>22</v>
+      </c>
+      <c r="E33">
+        <v>-1</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="G33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>115</v>
+      </c>
+      <c r="B34" t="s">
+        <v>112</v>
+      </c>
+      <c r="C34" t="s">
+        <v>70</v>
+      </c>
+      <c r="D34" t="s">
+        <v>22</v>
+      </c>
+      <c r="E34">
+        <v>-1</v>
+      </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>116</v>
+      </c>
+      <c r="B35" t="s">
+        <v>113</v>
+      </c>
+      <c r="C35" t="s">
+        <v>70</v>
+      </c>
+      <c r="D35" t="s">
+        <v>22</v>
+      </c>
+      <c r="E35">
+        <v>-1</v>
+      </c>
+      <c r="F35">
+        <v>0</v>
+      </c>
+      <c r="G35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>117</v>
+      </c>
+      <c r="B36" t="s">
+        <v>114</v>
+      </c>
+      <c r="C36" t="s">
+        <v>70</v>
+      </c>
+      <c r="D36" t="s">
+        <v>22</v>
+      </c>
+      <c r="E36">
+        <v>-1</v>
+      </c>
+      <c r="F36">
+        <v>0</v>
+      </c>
+      <c r="G36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>118</v>
+      </c>
+      <c r="B37" t="s">
+        <v>115</v>
+      </c>
+      <c r="C37" t="s">
+        <v>70</v>
+      </c>
+      <c r="D37" t="s">
+        <v>22</v>
+      </c>
+      <c r="E37">
+        <v>-1</v>
+      </c>
+      <c r="F37">
+        <v>0</v>
+      </c>
+      <c r="G37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>119</v>
+      </c>
+      <c r="B38" t="s">
+        <v>116</v>
+      </c>
+      <c r="C38" t="s">
+        <v>70</v>
+      </c>
+      <c r="D38" t="s">
+        <v>22</v>
+      </c>
+      <c r="E38">
+        <v>-1</v>
+      </c>
+      <c r="F38">
+        <v>0</v>
+      </c>
+      <c r="G38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>120</v>
+      </c>
+      <c r="B39" t="s">
+        <v>117</v>
+      </c>
+      <c r="C39" t="s">
+        <v>70</v>
+      </c>
+      <c r="D39" t="s">
+        <v>22</v>
+      </c>
+      <c r="E39">
+        <v>-1</v>
+      </c>
+      <c r="F39">
+        <v>0</v>
+      </c>
+      <c r="G39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>121</v>
+      </c>
+      <c r="B40" t="s">
+        <v>118</v>
+      </c>
+      <c r="C40" t="s">
+        <v>70</v>
+      </c>
+      <c r="D40" t="s">
+        <v>22</v>
+      </c>
+      <c r="E40">
+        <v>-1</v>
+      </c>
+      <c r="F40">
+        <v>0</v>
+      </c>
+      <c r="G40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>122</v>
+      </c>
+      <c r="B41" t="s">
+        <v>119</v>
+      </c>
+      <c r="C41" t="s">
+        <v>70</v>
+      </c>
+      <c r="D41" t="s">
+        <v>22</v>
+      </c>
+      <c r="E41">
+        <v>-1</v>
+      </c>
+      <c r="F41">
+        <v>0</v>
+      </c>
+      <c r="G41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>123</v>
+      </c>
+      <c r="B42" t="s">
+        <v>120</v>
+      </c>
+      <c r="C42" t="s">
+        <v>70</v>
+      </c>
+      <c r="D42" t="s">
+        <v>22</v>
+      </c>
+      <c r="E42">
+        <v>-1</v>
+      </c>
+      <c r="F42">
+        <v>0</v>
+      </c>
+      <c r="G42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>124</v>
+      </c>
+      <c r="B43" t="s">
+        <v>121</v>
+      </c>
+      <c r="C43" t="s">
+        <v>70</v>
+      </c>
+      <c r="D43" t="s">
+        <v>22</v>
+      </c>
+      <c r="E43">
+        <v>-1</v>
+      </c>
+      <c r="F43">
+        <v>0</v>
+      </c>
+      <c r="G43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>125</v>
+      </c>
+      <c r="B44" t="s">
+        <v>122</v>
+      </c>
+      <c r="C44" t="s">
+        <v>70</v>
+      </c>
+      <c r="D44" t="s">
+        <v>22</v>
+      </c>
+      <c r="E44">
+        <v>-1</v>
+      </c>
+      <c r="F44">
+        <v>0</v>
+      </c>
+      <c r="G44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>126</v>
+      </c>
+      <c r="B45" t="s">
+        <v>123</v>
+      </c>
+      <c r="C45" t="s">
+        <v>70</v>
+      </c>
+      <c r="D45" t="s">
+        <v>22</v>
+      </c>
+      <c r="E45">
+        <v>-1</v>
+      </c>
+      <c r="F45">
+        <v>0</v>
+      </c>
+      <c r="G45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>127</v>
+      </c>
+      <c r="B46" t="s">
+        <v>124</v>
+      </c>
+      <c r="C46" t="s">
+        <v>70</v>
+      </c>
+      <c r="D46" t="s">
+        <v>22</v>
+      </c>
+      <c r="E46">
+        <v>-1</v>
+      </c>
+      <c r="F46">
+        <v>0</v>
+      </c>
+      <c r="G46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>128</v>
+      </c>
+      <c r="B47" t="s">
+        <v>125</v>
+      </c>
+      <c r="C47" t="s">
+        <v>70</v>
+      </c>
+      <c r="D47" t="s">
+        <v>22</v>
+      </c>
+      <c r="E47">
+        <v>-1</v>
+      </c>
+      <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>129</v>
+      </c>
+      <c r="B48" t="s">
+        <v>126</v>
+      </c>
+      <c r="C48" t="s">
+        <v>70</v>
+      </c>
+      <c r="D48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E48">
+        <v>-1</v>
+      </c>
+      <c r="F48">
+        <v>0</v>
+      </c>
+      <c r="G48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>130</v>
+      </c>
+      <c r="B49" t="s">
+        <v>127</v>
+      </c>
+      <c r="C49" t="s">
+        <v>70</v>
+      </c>
+      <c r="D49" t="s">
+        <v>22</v>
+      </c>
+      <c r="E49">
+        <v>-1</v>
+      </c>
+      <c r="F49">
+        <v>0</v>
+      </c>
+      <c r="G49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>131</v>
+      </c>
+      <c r="B50" t="s">
+        <v>128</v>
+      </c>
+      <c r="C50" t="s">
+        <v>70</v>
+      </c>
+      <c r="D50" t="s">
+        <v>22</v>
+      </c>
+      <c r="E50">
+        <v>-1</v>
+      </c>
+      <c r="F50">
+        <v>0</v>
+      </c>
+      <c r="G50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>132</v>
+      </c>
+      <c r="B51" t="s">
+        <v>129</v>
+      </c>
+      <c r="C51" t="s">
+        <v>70</v>
+      </c>
+      <c r="D51" t="s">
+        <v>22</v>
+      </c>
+      <c r="E51">
+        <v>-1</v>
+      </c>
+      <c r="F51">
+        <v>0</v>
+      </c>
+      <c r="G51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>133</v>
+      </c>
+      <c r="B52" t="s">
+        <v>130</v>
+      </c>
+      <c r="C52" t="s">
+        <v>70</v>
+      </c>
+      <c r="D52" t="s">
+        <v>22</v>
+      </c>
+      <c r="E52">
+        <v>-1</v>
+      </c>
+      <c r="F52">
+        <v>0</v>
+      </c>
+      <c r="G52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>134</v>
+      </c>
+      <c r="B53" t="s">
+        <v>131</v>
+      </c>
+      <c r="C53" t="s">
+        <v>70</v>
+      </c>
+      <c r="D53" t="s">
+        <v>22</v>
+      </c>
+      <c r="E53">
+        <v>-1</v>
+      </c>
+      <c r="F53">
+        <v>0</v>
+      </c>
+      <c r="G53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>135</v>
+      </c>
+      <c r="B54" t="s">
+        <v>132</v>
+      </c>
+      <c r="C54" t="s">
+        <v>70</v>
+      </c>
+      <c r="D54" t="s">
+        <v>22</v>
+      </c>
+      <c r="E54">
+        <v>-1</v>
+      </c>
+      <c r="F54">
+        <v>0</v>
+      </c>
+      <c r="G54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>136</v>
+      </c>
+      <c r="B55" t="s">
+        <v>133</v>
+      </c>
+      <c r="C55" t="s">
+        <v>70</v>
+      </c>
+      <c r="D55" t="s">
+        <v>22</v>
+      </c>
+      <c r="E55">
+        <v>-1</v>
+      </c>
+      <c r="F55">
+        <v>0</v>
+      </c>
+      <c r="G55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>137</v>
+      </c>
+      <c r="B56" t="s">
+        <v>134</v>
+      </c>
+      <c r="C56" t="s">
+        <v>70</v>
+      </c>
+      <c r="D56" t="s">
+        <v>22</v>
+      </c>
+      <c r="E56">
+        <v>-1</v>
+      </c>
+      <c r="F56">
+        <v>0</v>
+      </c>
+      <c r="G56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>138</v>
+      </c>
+      <c r="B57" t="s">
+        <v>135</v>
+      </c>
+      <c r="C57" t="s">
+        <v>70</v>
+      </c>
+      <c r="D57" t="s">
+        <v>22</v>
+      </c>
+      <c r="E57">
+        <v>-1</v>
+      </c>
+      <c r="F57">
+        <v>0</v>
+      </c>
+      <c r="G57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>139</v>
+      </c>
+      <c r="B58" t="s">
+        <v>136</v>
+      </c>
+      <c r="C58" t="s">
+        <v>70</v>
+      </c>
+      <c r="D58" t="s">
+        <v>22</v>
+      </c>
+      <c r="E58">
+        <v>-1</v>
+      </c>
+      <c r="F58">
+        <v>0</v>
+      </c>
+      <c r="G58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>140</v>
+      </c>
+      <c r="B59" t="s">
+        <v>137</v>
+      </c>
+      <c r="C59" t="s">
+        <v>70</v>
+      </c>
+      <c r="D59" t="s">
+        <v>22</v>
+      </c>
+      <c r="E59">
+        <v>-1</v>
+      </c>
+      <c r="F59">
+        <v>0</v>
+      </c>
+      <c r="G59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>141</v>
+      </c>
+      <c r="B60" t="s">
+        <v>138</v>
+      </c>
+      <c r="C60" t="s">
+        <v>70</v>
+      </c>
+      <c r="D60" t="s">
+        <v>22</v>
+      </c>
+      <c r="E60">
+        <v>-1</v>
+      </c>
+      <c r="F60">
+        <v>0</v>
+      </c>
+      <c r="G60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>142</v>
+      </c>
+      <c r="B61" t="s">
+        <v>139</v>
+      </c>
+      <c r="C61" t="s">
+        <v>70</v>
+      </c>
+      <c r="D61" t="s">
+        <v>22</v>
+      </c>
+      <c r="E61">
+        <v>-1</v>
+      </c>
+      <c r="F61">
+        <v>0</v>
+      </c>
+      <c r="G61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>143</v>
+      </c>
+      <c r="B62" t="s">
+        <v>140</v>
+      </c>
+      <c r="C62" t="s">
+        <v>70</v>
+      </c>
+      <c r="D62" t="s">
+        <v>22</v>
+      </c>
+      <c r="E62">
+        <v>-1</v>
+      </c>
+      <c r="F62">
+        <v>0</v>
+      </c>
+      <c r="G62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>144</v>
+      </c>
+      <c r="B63" t="s">
+        <v>141</v>
+      </c>
+      <c r="C63" t="s">
+        <v>70</v>
+      </c>
+      <c r="D63" t="s">
+        <v>22</v>
+      </c>
+      <c r="E63">
+        <v>-1</v>
+      </c>
+      <c r="F63">
+        <v>0</v>
+      </c>
+      <c r="G63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>145</v>
+      </c>
+      <c r="B64" t="s">
+        <v>142</v>
+      </c>
+      <c r="C64" t="s">
+        <v>70</v>
+      </c>
+      <c r="D64" t="s">
+        <v>22</v>
+      </c>
+      <c r="E64">
+        <v>-1</v>
+      </c>
+      <c r="F64">
+        <v>0</v>
+      </c>
+      <c r="G64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>146</v>
+      </c>
+      <c r="B65" t="s">
+        <v>143</v>
+      </c>
+      <c r="C65" t="s">
+        <v>70</v>
+      </c>
+      <c r="D65" t="s">
+        <v>22</v>
+      </c>
+      <c r="E65">
+        <v>-1</v>
+      </c>
+      <c r="F65">
+        <v>0</v>
+      </c>
+      <c r="G65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>147</v>
+      </c>
+      <c r="B66" t="s">
+        <v>144</v>
+      </c>
+      <c r="C66" t="s">
+        <v>70</v>
+      </c>
+      <c r="D66" t="s">
+        <v>22</v>
+      </c>
+      <c r="E66">
+        <v>-1</v>
+      </c>
+      <c r="F66">
+        <v>0</v>
+      </c>
+      <c r="G66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>148</v>
+      </c>
+      <c r="B67" t="s">
+        <v>145</v>
+      </c>
+      <c r="C67" t="s">
+        <v>70</v>
+      </c>
+      <c r="D67" t="s">
+        <v>22</v>
+      </c>
+      <c r="E67">
+        <v>-1</v>
+      </c>
+      <c r="F67">
+        <v>0</v>
+      </c>
+      <c r="G67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>149</v>
+      </c>
+      <c r="B68" t="s">
+        <v>146</v>
+      </c>
+      <c r="C68" t="s">
+        <v>70</v>
+      </c>
+      <c r="D68" t="s">
+        <v>22</v>
+      </c>
+      <c r="E68">
+        <v>-1</v>
+      </c>
+      <c r="F68">
+        <v>0</v>
+      </c>
+      <c r="G68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>150</v>
+      </c>
+      <c r="B69" t="s">
+        <v>147</v>
+      </c>
+      <c r="C69" t="s">
+        <v>70</v>
+      </c>
+      <c r="D69" t="s">
+        <v>22</v>
+      </c>
+      <c r="E69">
+        <v>-1</v>
+      </c>
+      <c r="F69">
+        <v>0</v>
+      </c>
+      <c r="G69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>151</v>
+      </c>
+      <c r="B70" t="s">
+        <v>148</v>
+      </c>
+      <c r="C70" t="s">
+        <v>70</v>
+      </c>
+      <c r="D70" t="s">
+        <v>22</v>
+      </c>
+      <c r="E70">
+        <v>-1</v>
+      </c>
+      <c r="F70">
+        <v>0</v>
+      </c>
+      <c r="G70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>152</v>
+      </c>
+      <c r="B71" t="s">
+        <v>149</v>
+      </c>
+      <c r="C71" t="s">
+        <v>70</v>
+      </c>
+      <c r="D71" t="s">
+        <v>22</v>
+      </c>
+      <c r="E71">
+        <v>-1</v>
+      </c>
+      <c r="F71">
+        <v>0</v>
+      </c>
+      <c r="G71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>153</v>
+      </c>
+      <c r="B72" t="s">
+        <v>150</v>
+      </c>
+      <c r="C72" t="s">
+        <v>70</v>
+      </c>
+      <c r="D72" t="s">
+        <v>22</v>
+      </c>
+      <c r="E72">
+        <v>-1</v>
+      </c>
+      <c r="F72">
+        <v>0</v>
+      </c>
+      <c r="G72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>154</v>
+      </c>
+      <c r="B73" t="s">
+        <v>151</v>
+      </c>
+      <c r="C73" t="s">
+        <v>70</v>
+      </c>
+      <c r="D73" t="s">
+        <v>22</v>
+      </c>
+      <c r="E73">
+        <v>-1</v>
+      </c>
+      <c r="F73">
+        <v>0</v>
+      </c>
+      <c r="G73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>155</v>
+      </c>
+      <c r="B74" t="s">
+        <v>152</v>
+      </c>
+      <c r="C74" t="s">
+        <v>70</v>
+      </c>
+      <c r="D74" t="s">
+        <v>22</v>
+      </c>
+      <c r="E74">
+        <v>-1</v>
+      </c>
+      <c r="F74">
+        <v>0</v>
+      </c>
+      <c r="G74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>156</v>
+      </c>
+      <c r="B75" t="s">
+        <v>153</v>
+      </c>
+      <c r="C75" t="s">
+        <v>70</v>
+      </c>
+      <c r="D75" t="s">
+        <v>22</v>
+      </c>
+      <c r="E75">
+        <v>-1</v>
+      </c>
+      <c r="F75">
+        <v>0</v>
+      </c>
+      <c r="G75">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>157</v>
+      </c>
+      <c r="B76" t="s">
+        <v>154</v>
+      </c>
+      <c r="C76" t="s">
+        <v>70</v>
+      </c>
+      <c r="D76" t="s">
+        <v>22</v>
+      </c>
+      <c r="E76">
+        <v>-1</v>
+      </c>
+      <c r="F76">
+        <v>0</v>
+      </c>
+      <c r="G76">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>158</v>
+      </c>
+      <c r="B77" t="s">
+        <v>155</v>
+      </c>
+      <c r="C77" t="s">
+        <v>70</v>
+      </c>
+      <c r="D77" t="s">
+        <v>22</v>
+      </c>
+      <c r="E77">
+        <v>-1</v>
+      </c>
+      <c r="F77">
+        <v>0</v>
+      </c>
+      <c r="G77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>159</v>
+      </c>
+      <c r="B78" t="s">
+        <v>156</v>
+      </c>
+      <c r="C78" t="s">
+        <v>70</v>
+      </c>
+      <c r="D78" t="s">
+        <v>22</v>
+      </c>
+      <c r="E78">
+        <v>-1</v>
+      </c>
+      <c r="F78">
+        <v>0</v>
+      </c>
+      <c r="G78">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>160</v>
+      </c>
+      <c r="B79" t="s">
+        <v>157</v>
+      </c>
+      <c r="C79" t="s">
+        <v>70</v>
+      </c>
+      <c r="D79" t="s">
+        <v>22</v>
+      </c>
+      <c r="E79">
+        <v>-1</v>
+      </c>
+      <c r="F79">
+        <v>0</v>
+      </c>
+      <c r="G79">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>161</v>
+      </c>
+      <c r="B80" t="s">
+        <v>158</v>
+      </c>
+      <c r="C80" t="s">
+        <v>70</v>
+      </c>
+      <c r="D80" t="s">
+        <v>22</v>
+      </c>
+      <c r="E80">
+        <v>-1</v>
+      </c>
+      <c r="F80">
+        <v>0</v>
+      </c>
+      <c r="G80">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>162</v>
+      </c>
+      <c r="B81" t="s">
+        <v>159</v>
+      </c>
+      <c r="C81" t="s">
+        <v>70</v>
+      </c>
+      <c r="D81" t="s">
+        <v>22</v>
+      </c>
+      <c r="E81">
+        <v>-1</v>
+      </c>
+      <c r="F81">
+        <v>0</v>
+      </c>
+      <c r="G81">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>163</v>
+      </c>
+      <c r="B82" t="s">
+        <v>160</v>
+      </c>
+      <c r="C82" t="s">
+        <v>70</v>
+      </c>
+      <c r="D82" t="s">
+        <v>22</v>
+      </c>
+      <c r="E82">
+        <v>-1</v>
+      </c>
+      <c r="F82">
+        <v>0</v>
+      </c>
+      <c r="G82">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>164</v>
+      </c>
+      <c r="B83" t="s">
+        <v>161</v>
+      </c>
+      <c r="C83" t="s">
+        <v>70</v>
+      </c>
+      <c r="D83" t="s">
+        <v>22</v>
+      </c>
+      <c r="E83">
+        <v>-1</v>
+      </c>
+      <c r="F83">
+        <v>0</v>
+      </c>
+      <c r="G83">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
         <v>1000</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B84" t="s">
         <v>66</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C84" t="s">
         <v>67</v>
       </c>
-      <c r="D25">
-        <v>-1</v>
-      </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-      <c r="F25">
-        <v>-1</v>
-      </c>
-      <c r="G25">
-        <v>0</v>
-      </c>
-      <c r="H25" t="s">
+      <c r="D84">
+        <v>-1</v>
+      </c>
+      <c r="E84">
+        <v>19</v>
+      </c>
+      <c r="F84">
+        <v>-1</v>
+      </c>
+      <c r="G84">
+        <v>0</v>
+      </c>
+      <c r="H84" t="s">
         <v>68</v>
       </c>
     </row>
